--- a/analysis/data/raw_data/Dungeness_sppcomp_data_2023_FINAL_KSupdate03012024.xlsx
+++ b/analysis/data/raw_data/Dungeness_sppcomp_data_2023_FINAL_KSupdate03012024.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/kathryn_sutton_dfw_wa_gov/Documents/Documents/Projects/Dungeness_sppcomp/2023/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stateofwa-my.sharepoint.com/personal/kevin_see_dfw_wa_gov/Documents/Documents/Git/MyProjects/DungenessSonar/analysis/data/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA69926B-D091-45D9-A496-A35701557310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{CA69926B-D091-45D9-A496-A35701557310}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AAC84170-1AD0-43E6-BFF4-DD699A738A1D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{52477DB6-A063-41C8-A0DE-E1317ED7D466}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{52477DB6-A063-41C8-A0DE-E1317ED7D466}"/>
   </bookViews>
   <sheets>
     <sheet name="2023" sheetId="4" r:id="rId1"/>
     <sheet name="2022" sheetId="1" r:id="rId2"/>
     <sheet name="2021" sheetId="5" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" concurrentCalc="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2578,9 +2578,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2618,7 +2618,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2724,7 +2724,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2866,7 +2866,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2896,15 +2896,15 @@
     <col min="11" max="11" width="8.90625" style="2" customWidth="1"/>
     <col min="12" max="13" width="13" style="2" customWidth="1"/>
     <col min="14" max="14" width="9.453125" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.6328125" style="2" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6328125" style="2" customWidth="1"/>
     <col min="16" max="16" width="12.453125" style="2" customWidth="1"/>
-    <col min="17" max="17" width="8.90625" style="2" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="8.90625" style="2" customWidth="1"/>
     <col min="18" max="19" width="15.36328125" style="2" customWidth="1"/>
     <col min="20" max="20" width="17.36328125" style="2" customWidth="1"/>
     <col min="21" max="21" width="8.90625" style="2" customWidth="1"/>
     <col min="22" max="22" width="20" style="2" customWidth="1"/>
     <col min="23" max="23" width="13.36328125" style="2" customWidth="1"/>
-    <col min="24" max="27" width="19.36328125" style="2" hidden="1" customWidth="1"/>
+    <col min="24" max="27" width="19.36328125" style="2" customWidth="1"/>
     <col min="28" max="28" width="31.81640625" style="3" customWidth="1"/>
     <col min="29" max="29" width="18.36328125" style="2" customWidth="1"/>
     <col min="30" max="30" width="8.90625" style="2"/>
